--- a/Configuración de experimentos y estructura de paper.xlsx
+++ b/Configuración de experimentos y estructura de paper.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\OneDrive\Documentos\GitHub\KP_Analysis_Binarization_Schemes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E62CECA5-014C-4CD8-9BFC-3F776C65816A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE80DCC-8755-43AD-AF9D-BC14996152C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{A8485A2D-61EC-4FE9-9F49-A0C78C73A146}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" activeTab="3" xr2:uid="{A8485A2D-61EC-4FE9-9F49-A0C78C73A146}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="estructura paper" sheetId="4" r:id="rId2"/>
+    <sheet name="seteo de parámetros" sheetId="2" r:id="rId3"/>
+    <sheet name="contexto experimental" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>Instancia</t>
   </si>
@@ -264,13 +267,64 @@
   </si>
   <si>
     <t>Conclusiones</t>
+  </si>
+  <si>
+    <t>poblacion</t>
+  </si>
+  <si>
+    <t>iteraciones</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+  <si>
+    <t>RB</t>
+  </si>
+  <si>
+    <t>MH</t>
+  </si>
+  <si>
+    <t>contexto</t>
+  </si>
+  <si>
+    <t>valor</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>X4</t>
+  </si>
+  <si>
+    <t>Z1</t>
+  </si>
+  <si>
+    <t>Z2</t>
+  </si>
+  <si>
+    <t>Z3</t>
+  </si>
+  <si>
+    <t>Z4</t>
+  </si>
+  <si>
+    <t>vamos a probar tambien las nuevas funciones de transferencias para argumentar su funcionamiento</t>
+  </si>
+  <si>
+    <t>acá incorpora todo tu análisis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,13 +332,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -340,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -348,17 +414,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -694,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B0B2F3-632D-4750-962A-3D587FBEC826}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -703,11 +787,11 @@
     <col min="6" max="6" width="11.5546875" style="2"/>
     <col min="7" max="7" width="18.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="11.5546875" style="2"/>
-    <col min="10" max="12" width="11.5546875" style="6"/>
+    <col min="10" max="12" width="11.5546875" style="4"/>
     <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,7 +808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -737,11 +821,11 @@
       <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -754,11 +838,11 @@
       <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -771,11 +855,11 @@
       <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -790,7 +874,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -801,7 +885,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -816,7 +900,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,7 +917,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -850,7 +934,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,7 +951,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -882,7 +966,7 @@
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -897,7 +981,7 @@
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -912,7 +996,7 @@
       </c>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -926,11 +1010,8 @@
         <v>40</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="J14" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -944,14 +1025,8 @@
         <v>41</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="J15" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -961,11 +1036,8 @@
       <c r="C16" s="1">
         <v>100</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -975,11 +1047,8 @@
       <c r="C17" s="1">
         <v>200</v>
       </c>
-      <c r="K17" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -989,11 +1058,8 @@
       <c r="C18" s="1">
         <v>500</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1003,14 +1069,12 @@
       <c r="C19" s="1">
         <v>1000</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1020,11 +1084,12 @@
       <c r="C20" s="1">
         <v>2000</v>
       </c>
-      <c r="K20" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1034,15 +1099,12 @@
       <c r="C21" s="1">
         <v>5000</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="4"/>
-      <c r="K21" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F21" s="8"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1052,100 +1114,40 @@
       <c r="C22" s="1">
         <v>10000</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="1">
-        <v>21</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="1">
-        <v>2</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24" s="1">
-        <v>24</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="1">
-        <v>31</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="1">
-        <f>H25*H24*H23*H22</f>
-        <v>31248</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K27" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K28" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K29" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J30" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J31" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1153,4 +1155,673 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CBAF3D2-B114-4909-8093-8962E5EE4DDB}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="14"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86176665-CB6F-4EB3-B44A-0671C7C942BB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B99E1C3F-B2BE-4D34-A310-8146D6E6719E}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="9">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>9147</v>
+      </c>
+      <c r="E2" s="1">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="9">
+        <v>100</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>11238</v>
+      </c>
+      <c r="E3" s="1">
+        <v>200</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="9">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>28857</v>
+      </c>
+      <c r="E4" s="1">
+        <v>500</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="J4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1">
+        <v>54503</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="7"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1">
+        <v>110625</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="J6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1">
+        <v>276457</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="J7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>563647</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="J8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1">
+        <f>K7*K6*K5*K4</f>
+        <v>62496</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1514</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1634</v>
+      </c>
+      <c r="E10" s="1">
+        <v>200</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4566</v>
+      </c>
+      <c r="E11" s="1">
+        <v>500</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9052</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1">
+        <v>18051</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1">
+        <v>44356</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1">
+        <v>90204</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2397</v>
+      </c>
+      <c r="E16" s="1">
+        <v>100</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2697</v>
+      </c>
+      <c r="E17" s="1">
+        <v>200</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7117</v>
+      </c>
+      <c r="E18" s="1">
+        <v>500</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1">
+        <v>14390</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1">
+        <v>28919</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1">
+        <v>72505</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="1">
+        <v>146919</v>
+      </c>
+      <c r="E22" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J3:K3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>